--- a/data/trans_orig/P41C_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P41C_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han tenido o tienen dificultades para tener un embarazo en 2023</t>
+          <t>Población según si han tenido o tienen dificultades para tener un embarazo en 2023 (tasa de respuesta: 87,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>57682</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59583</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>62536</t>
+          <t>62090</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>121583</t>
+          <t>121838</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1901</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1338</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1901</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3435</t>
+          <t>3881</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3970</t>
+          <t>3715</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1901</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1338</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1901</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1338</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52436</t>
+          <t>52445</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>56074</t>
+          <t>57336</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>113644</t>
+          <t>113530</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>123182</t>
+          <t>123139</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2821</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1987</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8300</t>
+          <t>6411</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>148</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7733</t>
+          <t>8218</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6897</t>
+          <t>7683</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5217</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8621</t>
+          <t>8846</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2821</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1987</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>62274</t>
+          <t>62004</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>72269</t>
+          <t>72831</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>64382</t>
+          <t>64631</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>72379</t>
+          <t>72628</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>130832</t>
+          <t>130874</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>143205</t>
+          <t>143498</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,37%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1668</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1938</t>
+          <t>1924</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11263</t>
+          <t>11447</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>1801</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7669</t>
+          <t>8067</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4875</t>
+          <t>4596</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16103</t>
+          <t>15920</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1668</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6235</t>
+          <t>6562</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5822</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>1198</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8400</t>
+          <t>8531</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>53173</t>
+          <t>48644</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>60833</t>
+          <t>60652</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>67995</t>
+          <t>68367</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>115419</t>
+          <t>116859</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>132801</t>
+          <t>132969</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3199</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4378</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4151</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3199</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5768</t>
+          <t>6743</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6577</t>
+          <t>5924</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3199</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1569</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13815</t>
+          <t>18344</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5192</t>
+          <t>5112</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1746</t>
+          <t>1551</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>19498</t>
+          <t>16846</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>12,33%</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>49978</t>
+          <t>48362</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>65056</t>
+          <t>65297</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>116762</t>
+          <t>116927</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>121112</t>
+          <t>121107</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1787</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1809</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1079</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3130</t>
+          <t>2888</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2445</t>
+          <t>3025</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2877</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3994</t>
+          <t>4550</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>70812</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>72506</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>58885</t>
+          <t>58502</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>63867</t>
+          <t>63851</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>130529</t>
+          <t>130711</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>136345</t>
+          <t>136339</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1694</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3519</t>
+          <t>4163</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>3578</t>
+          <t>3574</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1694</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1694</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1694</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4355</t>
+          <t>5124</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5826</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>91132</t>
+          <t>91547</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>102574</t>
+          <t>102596</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>137842</t>
+          <t>138031</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>148227</t>
+          <t>148189</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>233140</t>
+          <t>231857</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>248416</t>
+          <t>248476</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,85%</t>
         </is>
       </c>
     </row>
@@ -4940,7 +4940,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>5355</t>
+          <t>6549</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>3974</t>
+          <t>3457</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>162</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>6927</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>9201</t>
+          <t>8763</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>3681</t>
+          <t>3341</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>12696</t>
+          <t>12504</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>5436</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>16858</t>
+          <t>16387</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>7963</t>
+          <t>6452</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>7726</t>
+          <t>6131</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>6837</t>
+          <t>7059</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>6184</t>
+          <t>5641</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>1068</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>10045</t>
+          <t>10114</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>367630</t>
+          <t>367253</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>126026</t>
+          <t>125937</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>134173</t>
+          <t>134128</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>499229</t>
+          <t>499657</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>518870</t>
+          <t>519112</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,83%</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5617,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>4163</t>
+          <t>3416</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>3953</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5707,7 +5707,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -5735,7 +5735,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>9093</t>
+          <t>9166</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>3705</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>9397</t>
+          <t>9535</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>3129</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>10687</t>
+          <t>8706</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>720</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>7633</t>
+          <t>8143</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>13306</t>
+          <t>12834</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>835103</t>
+          <t>835387</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>868457</t>
+          <t>869304</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>655429</t>
+          <t>655196</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>674208</t>
+          <t>673870</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>1498957</t>
+          <t>1499311</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>1541807</t>
+          <t>1539506</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>6119</t>
+          <t>4909</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>6941</t>
+          <t>6960</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>1565</t>
+          <t>1645</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>9164</t>
+          <t>10229</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -6412,12 +6412,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>4136</t>
+          <t>3991</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>22527</t>
+          <t>22468</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6427,12 +6427,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6447,12 +6447,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>9073</t>
+          <t>8951</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>21579</t>
+          <t>21715</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>15630</t>
+          <t>15135</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>39247</t>
+          <t>37965</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>11143</t>
+          <t>10833</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6545,7 +6545,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>6580</t>
+          <t>7260</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6580,7 +6580,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6595,12 +6595,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>11274</t>
+          <t>12024</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6610,12 +6610,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -6638,12 +6638,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>3449</t>
+          <t>3058</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>23006</t>
+          <t>23872</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>5791</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>17091</t>
+          <t>17290</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6688,47 +6688,47 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>2,49%</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>20368</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>10907</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>34389</t>
+        </is>
+      </c>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
           <t>0,69%</t>
         </is>
       </c>
-      <c r="P56" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="Q56" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R56" s="2" t="inlineStr">
-        <is>
-          <t>20368</t>
-        </is>
-      </c>
-      <c r="S56" s="2" t="inlineStr">
-        <is>
-          <t>10278</t>
-        </is>
-      </c>
-      <c r="T56" s="2" t="inlineStr">
-        <is>
-          <t>33807</t>
-        </is>
-      </c>
-      <c r="U56" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="V56" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P41C_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P41C_2023-Provincia-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>59583</t>
+          <t>59765</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -760,27 +760,27 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>64896</t>
+          <t>71375</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>62090</t>
+          <t>69143</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>65971</t>
+          <t>72407</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -795,27 +795,27 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>124478</t>
+          <t>131140</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>121838</t>
+          <t>128964</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>125553</t>
+          <t>132172</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3881</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3715</t>
+          <t>3208</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>59583</t>
+          <t>59765</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>59583</t>
+          <t>59765</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>59583</t>
+          <t>59765</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>65971</t>
+          <t>72407</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>65971</t>
+          <t>72407</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>65971</t>
+          <t>72407</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>125553</t>
+          <t>132172</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>125553</t>
+          <t>132172</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>125553</t>
+          <t>132172</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,27 +1407,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>59112</t>
+          <t>64048</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52445</t>
+          <t>57503</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62017</t>
+          <t>66940</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1442,27 +1442,27 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>61056</t>
+          <t>63498</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>57336</t>
+          <t>59048</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62360</t>
+          <t>65340</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>120168</t>
+          <t>127545</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>113530</t>
+          <t>120837</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>123139</t>
+          <t>130829</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1452</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6411</t>
+          <t>7453</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>749</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>4246</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1615</t>
+          <t>2184</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8218</t>
+          <t>7609</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1756,12 +1756,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7683</t>
+          <t>7361</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4828</t>
+          <t>6008</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2595</t>
+          <t>2550</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8846</t>
+          <t>7793</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>62017</t>
+          <t>66940</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>62017</t>
+          <t>66940</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>62017</t>
+          <t>66940</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>62360</t>
+          <t>65340</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>62360</t>
+          <t>65340</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>62360</t>
+          <t>65340</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>124377</t>
+          <t>132279</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>124377</t>
+          <t>132279</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>124377</t>
+          <t>132279</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>68754</t>
+          <t>67693</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>61170</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>72831</t>
+          <t>71706</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>69293</t>
+          <t>70477</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>64631</t>
+          <t>65609</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>72628</t>
+          <t>73778</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>138047</t>
+          <t>138171</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>130874</t>
+          <t>130919</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>143498</t>
+          <t>143555</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,01%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5143</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1791</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11447</t>
+          <t>10421</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3956</t>
+          <t>4712</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1801</t>
+          <t>2056</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8067</t>
+          <t>8990</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>9099</t>
+          <t>9629</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4596</t>
+          <t>5062</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15920</t>
+          <t>16230</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2551,12 +2551,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6562</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>623</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>5866</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>3288</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1198</t>
+          <t>1123</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8531</t>
+          <t>7633</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>75104</t>
+          <t>73788</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>75104</t>
+          <t>73788</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>75104</t>
+          <t>73788</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>75356</t>
+          <t>77299</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>75356</t>
+          <t>77299</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>75356</t>
+          <t>77299</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>150460</t>
+          <t>151088</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>150460</t>
+          <t>151088</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>150460</t>
+          <t>151088</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,27 +2771,27 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>62627</t>
+          <t>70962</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>48644</t>
+          <t>57138</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>66988</t>
+          <t>75884</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>65382</t>
+          <t>73073</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>60652</t>
+          <t>68177</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>68367</t>
+          <t>75834</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>128009</t>
+          <t>144034</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>116859</t>
+          <t>130545</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>132969</t>
+          <t>149733</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,6%</t>
         </is>
       </c>
     </row>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>870</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2929,12 +2929,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3779</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>870</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -2964,12 +2964,12 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4151</t>
+          <t>4621</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1795</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3042,12 +3042,12 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6743</t>
+          <t>6046</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1795</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
@@ -3077,12 +3077,12 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5924</t>
+          <t>7136</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>4361</t>
+          <t>4922</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>18344</t>
+          <t>18746</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1670</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -3268,12 +3268,12 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5112</t>
+          <t>5534</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6002</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>16846</t>
+          <t>21930</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>14,29%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>66988</t>
+          <t>75884</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>66988</t>
+          <t>75884</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>66988</t>
+          <t>75884</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>69617</t>
+          <t>77531</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>69617</t>
+          <t>77531</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>69617</t>
+          <t>77531</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>136605</t>
+          <t>153414</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>136605</t>
+          <t>153414</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>136605</t>
+          <t>153414</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,27 +3453,27 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>52161</t>
+          <t>59683</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>48362</t>
+          <t>56177</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>52855</t>
+          <t>60463</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3488,27 +3488,27 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>67668</t>
+          <t>76262</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>65297</t>
+          <t>73598</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>68604</t>
+          <t>77270</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>119830</t>
+          <t>135945</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>116927</t>
+          <t>132671</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>121107</t>
+          <t>137398</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>345</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -3611,12 +3611,12 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>345</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
@@ -3646,12 +3646,12 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1785</t>
+          <t>2083</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>663</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2888</t>
+          <t>3564</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>663</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3025</t>
+          <t>3480</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>780</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4493</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>780</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4550</t>
+          <t>4217</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>52855</t>
+          <t>60463</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>52855</t>
+          <t>60463</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>52855</t>
+          <t>60463</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>68604</t>
+          <t>77270</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>68604</t>
+          <t>77270</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>68604</t>
+          <t>77270</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>121459</t>
+          <t>137733</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>121459</t>
+          <t>137733</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>121459</t>
+          <t>137733</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>72506</t>
+          <t>75040</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>62349</t>
+          <t>63939</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>58502</t>
+          <t>59787</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>63851</t>
+          <t>65468</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>134855</t>
+          <t>138980</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>130711</t>
+          <t>135114</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>136339</t>
+          <t>141127</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>728</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -4293,12 +4293,12 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>4163</t>
+          <t>4162</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>728</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
@@ -4328,12 +4328,12 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>3574</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1419</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -4632,12 +4632,12 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>5124</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1419</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
@@ -4667,12 +4667,12 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>4829</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>72506</t>
+          <t>75040</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>72506</t>
+          <t>75040</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>72506</t>
+          <t>75040</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>64491</t>
+          <t>66086</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>64491</t>
+          <t>66086</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>64491</t>
+          <t>66086</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>136997</t>
+          <t>141127</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>136997</t>
+          <t>141127</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>136997</t>
+          <t>141127</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,32 +4817,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>97986</t>
+          <t>110730</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>91547</t>
+          <t>101785</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>102596</t>
+          <t>115384</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4852,32 +4852,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>143912</t>
+          <t>169260</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>138031</t>
+          <t>162557</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>148189</t>
+          <t>173483</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>241899</t>
+          <t>279989</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>231857</t>
+          <t>271088</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>248476</t>
+          <t>287068</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>96,04%</t>
         </is>
       </c>
     </row>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>6549</t>
+          <t>7171</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>709</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -4975,12 +4975,12 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>3574</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>1873</t>
+          <t>2967</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>710</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>8535</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>3218</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>8763</t>
+          <t>9234</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>6941</t>
+          <t>7239</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>3341</t>
+          <t>3608</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>12504</t>
+          <t>13037</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>10160</t>
+          <t>10615</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>5436</t>
+          <t>5717</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>16387</t>
+          <t>17644</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>6452</t>
+          <t>7763</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>6131</t>
+          <t>6490</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -5269,7 +5269,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>7059</t>
+          <t>7972</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,7 +5304,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>1782</t>
+          <t>1805</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>5641</t>
+          <t>6492</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>4007</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1068</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>10114</t>
+          <t>9557</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>105945</t>
+          <t>119877</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>105945</t>
+          <t>119877</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>105945</t>
+          <t>119877</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>153301</t>
+          <t>179012</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>153301</t>
+          <t>179012</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>153301</t>
+          <t>179012</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>259246</t>
+          <t>298889</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>259246</t>
+          <t>298889</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>259246</t>
+          <t>298889</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5499,69 +5499,69 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>380199</t>
+          <t>159278</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>367253</t>
+          <t>152316</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>384421</t>
+          <t>162815</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
+          <t>97,12%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>92,88%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>99,28%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>153945</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>147754</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>156900</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>97,03%</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>93,13%</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
           <t>98,9%</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>95,53%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>131284</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>125937</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>134128</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>96,83%</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>92,89%</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>98,93%</t>
-        </is>
-      </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
           <t>309</t>
@@ -5569,32 +5569,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>511483</t>
+          <t>313223</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>499657</t>
+          <t>304513</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>519112</t>
+          <t>318409</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>741</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3416</t>
+          <t>4410</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>741</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>3953</t>
+          <t>4068</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
@@ -5707,7 +5707,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>2162</t>
+          <t>2398</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -5735,12 +5735,12 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>9166</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5760,7 +5760,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>847</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3705</t>
+          <t>4655</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>2899</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>850</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>9535</t>
+          <t>9200</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -5961,12 +5961,12 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>8706</t>
+          <t>7944</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5986,32 +5986,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2875</t>
+          <t>3120</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>786</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>8143</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>5441</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1865</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>12834</t>
+          <t>13095</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -6064,17 +6064,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>384421</t>
+          <t>163998</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>384421</t>
+          <t>163998</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>384421</t>
+          <t>163998</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6099,17 +6099,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>135579</t>
+          <t>158652</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>135579</t>
+          <t>158652</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>135579</t>
+          <t>158652</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>520000</t>
+          <t>322650</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>520000</t>
+          <t>322650</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>520000</t>
+          <t>322650</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6181,32 +6181,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>852928</t>
+          <t>667199</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>835387</t>
+          <t>649949</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>869304</t>
+          <t>677410</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6216,32 +6216,32 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>665842</t>
+          <t>741827</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>655196</t>
+          <t>731327</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>673870</t>
+          <t>750506</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6251,32 +6251,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>1518768</t>
+          <t>1409027</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>1499311</t>
+          <t>1389789</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>1539506</t>
+          <t>1422551</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>96,81%</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -6304,57 +6304,57 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>7948</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>3393</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>1072</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>7932</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
           <t>0,14%</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>3225</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>1058</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>6960</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="O53" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6364,32 +6364,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>4433</t>
+          <t>5651</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>1645</t>
+          <t>2283</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>10229</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -6407,32 +6407,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>11975</t>
+          <t>12127</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>3991</t>
+          <t>6403</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>22468</t>
+          <t>21310</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6442,32 +6442,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>14668</t>
+          <t>16497</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>8951</t>
+          <t>10828</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>21715</t>
+          <t>24563</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6477,32 +6477,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>26643</t>
+          <t>28623</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>15135</t>
+          <t>19244</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>37965</t>
+          <t>38858</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -6520,7 +6520,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -6530,12 +6530,12 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>10833</t>
+          <t>9433</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -6545,7 +6545,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6555,7 +6555,7 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>1724</t>
+          <t>1756</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
@@ -6565,12 +6565,12 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>7260</t>
+          <t>6077</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
@@ -6580,7 +6580,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6590,27 +6590,27 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>4484</t>
+          <t>4475</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>1173</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>12024</t>
+          <t>11163</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -6633,32 +6633,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>10548</t>
+          <t>11451</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>3058</t>
+          <t>4693</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>23872</t>
+          <t>27644</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6668,32 +6668,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>9821</t>
+          <t>10124</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>5791</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>17290</t>
+          <t>17670</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6703,32 +6703,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>20368</t>
+          <t>21575</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>10907</t>
+          <t>13158</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>34389</t>
+          <t>36826</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -6746,17 +6746,17 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>879419</t>
+          <t>695755</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>879419</t>
+          <t>695755</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>879419</t>
+          <t>695755</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6781,17 +6781,17 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>695279</t>
+          <t>773596</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>695279</t>
+          <t>773596</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>695279</t>
+          <t>773596</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>1574697</t>
+          <t>1469352</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>1574697</t>
+          <t>1469352</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>1574697</t>
+          <t>1469352</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
